--- a/InputData/plcy-schd/FY/FY Future Years.xlsx
+++ b/InputData/plcy-schd/FY/FY Future Years.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\plcy-schd\FY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\plcy-schd\FY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA21A683-9523-4DE0-9A38-94035A233DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A11848-89A1-46A2-AED1-E86E1643D610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
